--- a/players.xlsx
+++ b/players.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\NetBeansProjects\FootballAuctionGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECEEAB8-AA93-44BE-B2B6-1F2E5013B402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673C60F8-C9F2-47F4-ADD4-F63A68D4321A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E8213422-0284-449A-843E-9F433E492A0A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>ID</t>
   </si>
@@ -67,6 +67,24 @@
   </si>
   <si>
     <t>CM</t>
+  </si>
+  <si>
+    <t>Cristiano Ronaldo</t>
+  </si>
+  <si>
+    <t>Kylian Mbappe</t>
+  </si>
+  <si>
+    <t>Erling Haaland</t>
+  </si>
+  <si>
+    <t>Kevin De Bruyne</t>
+  </si>
+  <si>
+    <t>MF</t>
+  </si>
+  <si>
+    <t>Vinicius Jr</t>
   </si>
 </sst>
 </file>
@@ -432,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC174790-4273-4BBA-936A-1699073DABCB}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" ht="29" x14ac:dyDescent="0.35">
@@ -503,6 +521,91 @@
         <v>90</v>
       </c>
     </row>
+    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2">
+        <v>94</v>
+      </c>
+      <c r="E5" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2">
+        <v>93</v>
+      </c>
+      <c r="E6" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2">
+        <v>92</v>
+      </c>
+      <c r="E7" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2">
+        <v>91</v>
+      </c>
+      <c r="E8" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2">
+        <v>90</v>
+      </c>
+      <c r="E9" s="2">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/players.xlsx
+++ b/players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\NetBeansProjects\FootballAuctionGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673C60F8-C9F2-47F4-ADD4-F63A68D4321A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E63B1C-EB83-4165-A9B0-B200E0FE9AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E8213422-0284-449A-843E-9F433E492A0A}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="8170" xr2:uid="{E8213422-0284-449A-843E-9F433E492A0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>ID</t>
   </si>
@@ -69,22 +69,19 @@
     <t>CM</t>
   </si>
   <si>
-    <t>Cristiano Ronaldo</t>
-  </si>
-  <si>
-    <t>Kylian Mbappe</t>
-  </si>
-  <si>
-    <t>Erling Haaland</t>
-  </si>
-  <si>
-    <t>Kevin De Bruyne</t>
-  </si>
-  <si>
     <t>MF</t>
   </si>
   <si>
     <t>Vinicius Jr</t>
+  </si>
+  <si>
+    <t>Ronaldo</t>
+  </si>
+  <si>
+    <t>Mbappe</t>
+  </si>
+  <si>
+    <t>De Bruyne</t>
   </si>
 </sst>
 </file>
@@ -521,12 +518,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
@@ -538,12 +535,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>6</v>
@@ -555,12 +552,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>6</v>
@@ -577,10 +574,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2">
         <v>91</v>
@@ -594,7 +591,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>6</v>
